--- a/site/Directory-ITSM-Integration-Guide/headings.xlsx
+++ b/site/Directory-ITSM-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,424 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>h_01KD7Y3KD9MT7413QHSHAVZCNF</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KD7Y3KD9MT7413QHSHAVZCNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Key Functions</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>h_01KV523N864ATFG7JMDXFT5DG6</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KV523N864ATFG7JMDXFT5DG6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01KV57ZG85Y9KNEXG8S288H3WK</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KV57ZG85Y9KNEXG8S288H3WK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Directory</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01KV57ZPHB45GVJ88EC0APPFJJ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KV57ZPHB45GVJ88EC0APPFJJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Directory Configuration</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KWEEAZ1QXZHB58W070R9Y9KB</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEEAZ1QXZHB58W070R9Y9KB</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Manage Writeback</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KWEJQQVVWW4SDBBB9P3WZAR7</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEJQQVVWW4SDBBB9P3WZAR7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Writeback Configuration</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KWEJRMA7Y1PT9Y45BG87AR5B</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEJRMA7Y1PT9Y45BG87AR5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Service Desk</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KWEJZ175DXK4E85QVHF0NRBX</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEJZ175DXK4E85QVHF0NRBX</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KWEK1FFDCXMHZW4GVW55XQEC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEK1FFDCXMHZW4GVW55XQEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ITSM Configuration</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KWEK2GH710TCT1JTNH7HK37K</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEK2GH710TCT1JTNH7HK37K</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Messaging Applications</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KWEK4GCZ5FWMB2G5GM4E7NZD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEK4GCZ5FWMB2G5GM4E7NZD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KWEK5VA7SPABDFPVA5R8ZHKJ</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEK5VA7SPABDFPVA5R8ZHKJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Directory-ITSM-Integration-Guide/headings.xlsx
+++ b/site/Directory-ITSM-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,86 +771,724 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>External User Ticketing</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KWEK5VA7SPABDFPVA5R8ZHKJ</t>
+          <t>h_01KWEK6CKKP9K68AHYZK8AQX1T</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEK5VA7SPABDFPVA5R8ZHKJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEK6CKKP9K68AHYZK8AQX1T</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Ticketing Configuration</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>h_01KWEK6XSKTWCC8DF71SJ3XQDP</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEK6XSKTWCC8DF71SJ3XQDP</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>External User Expiry Ext</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KWEMF2YRDGA9WBRXVQYE84D1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEMF2YRDGA9WBRXVQYE84D1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Expiry Notification</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KWEMWQ0KA22D6CVA502J7CAR</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEMWQ0KA22D6CVA502J7CAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Create Ticket</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KWEMZHDX3HW0204GPTF9EX87</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEMZHDX3HW0204GPTF9EX87</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Extend the Extension Period</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KWEN4EQY77ZRBDGRD4JJ3HMG</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEN4EQY77ZRBDGRD4JJ3HMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Access Fulfilment</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KWEN7ZGDWZF2FW8T48TZSBHP</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEN7ZGDWZF2FW8T48TZSBHP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Access Fulfillment Settings</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KWEN8ZD3FN8YRH7ASG4B82XK</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEN8ZD3FN8YRH7ASG4B82XK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KWEQ9V50JBM9GDK3DVNXFHVC</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQ9V50JBM9GDK3DVNXFHVC</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Naming</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KWEQA30HHS3MAR554WF8EPGY</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQA30HHS3MAR554WF8EPGY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Configure Username Format</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KWEQAKSVX3JJHQ7TZDK0ZFE9</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQAKSVX3JJHQ7TZDK0ZFE9</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Assignment</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KWEQFPS1GP3PP20VJSXD1WTW</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQFPS1GP3PP20VJSXD1WTW</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Organizational Unit (OU) Assignment Rules</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KWEQG3BCN8RKBYXC49PQPE5Y</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQG3BCN8RKBYXC49PQPE5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Assignment Rules</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KWEQJYDV5YBVKJH6DY81SX8Z</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQJYDV5YBVKJH6DY81SX8Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Groups Active Directory (Group Rules)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KWEQM679F8TVM219RF6MQ3VT</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQM679F8TVM219RF6MQ3VT</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Password Policy</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KWEQNJ20MXRPW1NF539BGKFC</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQNJ20MXRPW1NF539BGKFC</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Password Policy Configuration</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01KWEQP2GMXEQT9XC3YG8A0SPA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQP2GMXEQT9XC3YG8A0SPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01KWER6VNN0BAFH9WG64J126QX</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWER6VNN0BAFH9WG64J126QX</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01KWER73FFYP2KY20YANJSH6M5</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWER73FFYP2KY20YANJSH6M5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Define Notification Channel</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01KWER7NV99NHTZXVZTWAA35DR</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWER7NV99NHTZXVZTWAA35DR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Notification Configuration</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01KWERA0YBZKXJH6C73XBM54BK</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERA0YBZKXJH6C73XBM54BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Global Operational Settings</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01KWEREYS2MA70BX7DDADJYF6T</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEREYS2MA70BX7DDADJYF6T</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Logging Settings</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01KT6CZ6SK0CR6SJ6662M8E2VW</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KT6CZ6SK0CR6SJ6662M8E2VW</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01KT6CJQCS03KJD036GY6YNQJ7</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KT6CJQCS03KJD036GY6YNQJ7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Log Insights Settings</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>h_01KWEE98ZWSRZGSCZ44WB68AE5</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEE98ZWSRZGSCZ44WB68AE5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Source Filter Rules</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>h_01KWERHBRWQFKB7E87HNF5WT3V</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERHBRWQFKB7E87HNF5WT3V</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Operation Safeguard Settings</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>h_01KWERMQMEQNYXEHCGTMBYGSWJ</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERMQMEQNYXEHCGTMBYGSWJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Advanced Settings</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>h_01KWERQVHZCVABM2GYKRZ7Q0VT</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERQVHZCVABM2GYKRZ7Q0VT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>h_01KWEV0W0NMQ6MVWEQ64WSRBS8</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEV0W0NMQ6MVWEQ64WSRBS8</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Directory-ITSM-Integration-Guide/headings.xlsx
+++ b/site/Directory-ITSM-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1409,7 +1409,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1419,41 +1419,41 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01KWEV0W0NMQ6MVWEQ64WSRBS8</t>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEV0W0NMQ6MVWEQ64WSRBS8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1463,32 +1463,10 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Directory-ITSM-Integration-Guide/headings.xlsx
+++ b/site/Directory-ITSM-Integration-Guide/headings.xlsx
@@ -815,7 +815,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>External User Expiry Ext</t>
+          <t>External User Expiry Extension</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1265,85 +1265,85 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01KT6CZ6SK0CR6SJ6662M8E2VW</t>
+          <t>h_01KT6CJQCS03KJD036GY6YNQJ7</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KT6CZ6SK0CR6SJ6662M8E2VW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KT6CJQCS03KJD036GY6YNQJ7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01KT6CJQCS03KJD036GY6YNQJ7</t>
+          <t>h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KT6CJQCS03KJD036GY6YNQJ7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
+          <t>h_01KWEE98ZWSRZGSCZ44WB68AE5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEE98ZWSRZGSCZ44WB68AE5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Source Filter Rules</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01KWEE98ZWSRZGSCZ44WB68AE5</t>
+          <t>h_01KWERHBRWQFKB7E87HNF5WT3V</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEE98ZWSRZGSCZ44WB68AE5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERHBRWQFKB7E87HNF5WT3V</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Source Filter Rules</t>
+          <t>Operation Safeguard Settings</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1353,19 +1353,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01KWERHBRWQFKB7E87HNF5WT3V</t>
+          <t>h_01KWERMQMEQNYXEHCGTMBYGSWJ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERHBRWQFKB7E87HNF5WT3V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERMQMEQNYXEHCGTMBYGSWJ</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Operation Safeguard Settings</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1375,63 +1375,63 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01KWERMQMEQNYXEHCGTMBYGSWJ</t>
+          <t>h_01KWERQVHZCVABM2GYKRZ7Q0VT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERMQMEQNYXEHCGTMBYGSWJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERQVHZCVABM2GYKRZ7Q0VT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01KWERQVHZCVABM2GYKRZ7Q0VT</t>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERQVHZCVABM2GYKRZ7Q0VT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
     </row>

--- a/site/Directory-ITSM-Integration-Guide/headings.xlsx
+++ b/site/Directory-ITSM-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -947,29 +947,29 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rules</t>
+          <t>Manual Fulfillment</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KWEQ9V50JBM9GDK3DVNXFHVC</t>
+          <t>h_01M0FD1BRD4VTKZAWE4RV7TBHZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQ9V50JBM9GDK3DVNXFHVC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01M0FD1BRD4VTKZAWE4RV7TBHZ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Naming</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,41 +979,41 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KWEQA30HHS3MAR554WF8EPGY</t>
+          <t>h_01M0FDS5X1TRS2HQV78ZE1KEV2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQA30HHS3MAR554WF8EPGY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01M0FDS5X1TRS2HQV78ZE1KEV2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Configure Username Format</t>
+          <t>Rules</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KWEQAKSVX3JJHQ7TZDK0ZFE9</t>
+          <t>h_01KWEQ9V50JBM9GDK3DVNXFHVC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQAKSVX3JJHQ7TZDK0ZFE9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQ9V50JBM9GDK3DVNXFHVC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Naming</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KWEQFPS1GP3PP20VJSXD1WTW</t>
+          <t>h_01KWEQA30HHS3MAR554WF8EPGY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQFPS1GP3PP20VJSXD1WTW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQA30HHS3MAR554WF8EPGY</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Organizational Unit (OU) Assignment Rules</t>
+          <t>Configure Username Format</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,41 +1045,41 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KWEQG3BCN8RKBYXC49PQPE5Y</t>
+          <t>h_01KWEQAKSVX3JJHQ7TZDK0ZFE9</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQG3BCN8RKBYXC49PQPE5Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQAKSVX3JJHQ7TZDK0ZFE9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Assignment Rules</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KWEQJYDV5YBVKJH6DY81SX8Z</t>
+          <t>h_01KWEQFPS1GP3PP20VJSXD1WTW</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQJYDV5YBVKJH6DY81SX8Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQFPS1GP3PP20VJSXD1WTW</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Groups Active Directory (Group Rules)</t>
+          <t>Organizational Unit (OU) Assignment Rules</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,41 +1089,41 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KWEQM679F8TVM219RF6MQ3VT</t>
+          <t>h_01KWEQG3BCN8RKBYXC49PQPE5Y</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQM679F8TVM219RF6MQ3VT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQG3BCN8RKBYXC49PQPE5Y</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Assignment Rules</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KWEQNJ20MXRPW1NF539BGKFC</t>
+          <t>h_01KWEQJYDV5YBVKJH6DY81SX8Z</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQNJ20MXRPW1NF539BGKFC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQJYDV5YBVKJH6DY81SX8Z</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Password Policy Configuration</t>
+          <t>Groups Active Directory (Group Rules)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,107 +1133,107 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KWEQP2GMXEQT9XC3YG8A0SPA</t>
+          <t>h_01KWEQM679F8TVM219RF6MQ3VT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQP2GMXEQT9XC3YG8A0SPA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQM679F8TVM219RF6MQ3VT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KWER6VNN0BAFH9WG64J126QX</t>
+          <t>h_01KWEQNJ20MXRPW1NF539BGKFC</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWER6VNN0BAFH9WG64J126QX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQNJ20MXRPW1NF539BGKFC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Password Policy Configuration</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KWER73FFYP2KY20YANJSH6M5</t>
+          <t>h_01KWEQP2GMXEQT9XC3YG8A0SPA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWER73FFYP2KY20YANJSH6M5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQP2GMXEQT9XC3YG8A0SPA</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Define Notification Channel</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KWER7NV99NHTZXVZTWAA35DR</t>
+          <t>h_01KWER6VNN0BAFH9WG64J126QX</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWER7NV99NHTZXVZTWAA35DR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWER6VNN0BAFH9WG64J126QX</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Notification Configuration</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KWERA0YBZKXJH6C73XBM54BK</t>
+          <t>h_01KWER73FFYP2KY20YANJSH6M5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERA0YBZKXJH6C73XBM54BK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWER73FFYP2KY20YANJSH6M5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Global Operational Settings</t>
+          <t>Define Notification Channel</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1243,41 +1243,41 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01KWEREYS2MA70BX7DDADJYF6T</t>
+          <t>h_01KWER7NV99NHTZXVZTWAA35DR</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEREYS2MA70BX7DDADJYF6T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWER7NV99NHTZXVZTWAA35DR</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Individual Notifications (Per Record)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01KT6CJQCS03KJD036GY6YNQJ7</t>
+          <t>h_01KWERA0YBZKXJH6C73XBM54BK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KT6CJQCS03KJD036GY6YNQJ7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERA0YBZKXJH6C73XBM54BK</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Run Summary Notifications</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1287,85 +1287,85 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
+          <t>h_01M1BHSF1Q3TR6WSXNE8GV60WG</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01M1BHSF1Q3TR6WSXNE8GV60WG</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Global Operational Settings</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01KWEE98ZWSRZGSCZ44WB68AE5</t>
+          <t>h_01KWEREYS2MA70BX7DDADJYF6T</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEE98ZWSRZGSCZ44WB68AE5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEREYS2MA70BX7DDADJYF6T</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Source Filter Rules</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01KWERHBRWQFKB7E87HNF5WT3V</t>
+          <t>h_01M13VMATGG9BVY65KZH6PNP0R</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERHBRWQFKB7E87HNF5WT3V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01M13VMATGG9BVY65KZH6PNP0R</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Operation Safeguard Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01KWERMQMEQNYXEHCGTMBYGSWJ</t>
+          <t>h_01KT6CJQCS03KJD036GY6YNQJ7</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERMQMEQNYXEHCGTMBYGSWJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KT6CJQCS03KJD036GY6YNQJ7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1375,98 +1375,186 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01KWERQVHZCVABM2GYKRZ7Q0VT</t>
+          <t>h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERQVHZCVABM2GYKRZ7Q0VT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>h_01KWEE98ZWSRZGSCZ44WB68AE5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEE98ZWSRZGSCZ44WB68AE5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Source Filter Rules</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KWERHBRWQFKB7E87HNF5WT3V</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERHBRWQFKB7E87HNF5WT3V</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Operation Safeguard Settings</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KWERMQMEQNYXEHCGTMBYGSWJ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERMQMEQNYXEHCGTMBYGSWJ</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>Advanced Settings</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>h_01KWERQVHZCVABM2GYKRZ7Q0VT</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERQVHZCVABM2GYKRZ7Q0VT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
